--- a/files/九龙-将军澳-Park Seasons.xlsx
+++ b/files/九龙-将军澳-Park Seasons.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2A座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2B座 销控表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -112,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4984,7 +4847,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6042,7 +5905,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -11056,7 +10919,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -11102,7 +10965,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -11424,7 +11287,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -13264,7 +13127,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -15656,7 +15519,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -15794,7 +15657,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -28674,7 +28537,7 @@
       </c>
       <c r="G611" s="3" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H611" s="5" t="n">
@@ -32196,6481 +32059,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H55"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Park Seasons - 2A座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>335 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>331 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>66/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 437呎 (2房)
-$945万
-$21,629/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$1,015万
-$20,468/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$915万
-$20,199/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$882万
-$20,241/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$611万
-$18,969/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>F | 481呎 (2房)
-$1,014万
-$21,075/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H6" s="18" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>65/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 437呎 (2房)
-$757万
-$17,318/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$787万
-$15,861/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$685万
-$15,121/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$693万
-$15,888/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$511万
-$15,879/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>F | 481呎 (2房)
-$819万
-$17,019/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="H7" s="18" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>63/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 437呎 (2房)
-$756万
-$17,288/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$785万
-$15,829/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$684万
-$15,099/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$689万
-$15,796/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$513万
-$15,938/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>F | 481呎 (2房)
-$832万
-$17,297/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H8" s="18" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>62/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 437呎 (2房)
-$754万
-$17,256/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$784万
-$15,798/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$683万
-$15,077/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$684万
-$15,693/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$498万
-$15,469/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>F | 481呎 (2房)
-$781万
-$16,241/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H9" s="18" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>61/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 437呎 (2房)
-$753万
-$17,224/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$782万
-$15,768/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$698万
-$15,397/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$679万
-$15,571/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$508万
-$15,792/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>F | 481呎 (2房)
-$780万
-$16,208/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H10" s="18" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>60/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 437呎 (2房)
-$723万
-$16,551/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$772万
-$15,560/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$681万
-$15,033/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$675万
-$15,477/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$496万
-$15,413/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>F | 481呎 (2房)
-$778万
-$16,175/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H11" s="18" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>59/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 437呎 (2房)
-$750万
-$17,160/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$770万
-$15,530/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$680万
-$15,011/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$685万
-$15,706/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$507万
-$15,736/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>F | 481呎 (2房)
-$806万
-$16,765/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="H12" s="18" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>58/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 437呎 (2房)
-$749万
-$17,130/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$778万
-$15,677/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$679万
-$14,989/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$684万
-$15,681/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$506万
-$15,708/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>F | 481呎 (2房)
-$775万
-$16,114/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H13" s="18" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>57/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 437呎 (2房)
-$746万
-$17,066/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$766万
-$15,438/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$677万
-$14,949/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$666万
-$15,271/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$504万
-$15,649/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>F | 481呎 (2房)
-$802万
-$16,667/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H14" s="18" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>56/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 437呎 (2房)
-$745万
-$17,039/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$764万
-$15,407/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$676万
-$14,927/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$661万
-$15,154/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$503万
-$15,621/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>F | 481呎 (2房)
-$770万
-$16,012/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H15" s="18" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>55/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 437呎 (2房)
-$704万
-$16,121/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$763万
-$15,377/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$675万
-$14,905/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$660万
-$15,128/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$491万
-$15,245/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>F | 481呎 (2房)
-$769万
-$15,988/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H16" s="18" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>53/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 437呎 (2房)
-$695万
-$15,913/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$770万
-$15,520/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$674万
-$14,887/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$658万
-$15,096/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$498万
-$15,478/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>F | 481呎 (2房)
-$767万
-$15,954/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H17" s="18" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>52/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 437呎 (2房)
-$706万
-$16,156/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$803万
-$16,185/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$674万
-$14,868/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$657万
-$15,064/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$497万
-$15,447/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>F | 481呎 (2房)
-$766万
-$15,921/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H18" s="18" t="inlineStr"/>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>51/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 437呎 (2房)
-$705万
-$16,126/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$758万
-$15,286/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$672万
-$14,837/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$656万
-$15,034/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$496万
-$15,419/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>F | 481呎 (2房)
-$764万
-$15,886/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H19" s="18" t="inlineStr"/>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>50/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 437呎 (2房)
-$700万
-$16,009/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$800万
-$16,123/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$671万
-$14,806/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$654万
-$15,002/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$515万
-$15,994/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>F | 481呎 (2房)
-$763万
-$15,854/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H20" s="18" t="inlineStr"/>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>48/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$687万
-$15,333/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$755万
-$15,226/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$685万
-$15,119/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$660万
-$15,147/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$498万
-$15,450/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$528万
-$16,159/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$500万
-$15,382/呎
-(24年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>47/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$684万
-$15,272/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$752万
-$15,165/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$667万
-$14,720/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$650万
-$14,915/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$485万
-$15,050/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$499万
-$15,266/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$508万
-$15,646/呎
-(24年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>46/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$694万
-$15,500/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$759万
-$15,306/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$681万
-$15,024/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$649万
-$14,885/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$486万
-$15,106/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$499万
-$15,248/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="H23" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$496万
-$15,265/呎
-(24年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>45/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$685万
-$15,297/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$766万
-$15,448/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$664万
-$14,660/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$648万
-$14,853/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$486万
-$15,081/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$498万
-$15,232/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H24" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$506万
-$15,582/呎
-(24年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>43/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$684万
-$15,266/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$765万
-$15,417/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$663万
-$14,631/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$646万
-$14,826/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$482万
-$14,966/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$497万
-$15,205/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="H25" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$494万
-$15,206/呎
-(25年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$679万
-$15,147/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$746万
-$15,044/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$662万
-$14,609/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$645万
-$14,803/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$481万
-$14,938/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$499万
-$15,260/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$493万
-$15,172/呎
-(25年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$689万
-$15,377/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$753万
-$15,185/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$660万
-$14,581/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$644万
-$14,773/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$486万
-$15,078/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$498万
-$15,229/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="H27" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$492万
-$15,142/呎
-(25年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$680万
-$15,183/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$743万
-$14,984/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$659万
-$14,552/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$643万
-$14,743/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$479万
-$14,882/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="G28" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$497万
-$15,199/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="H28" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$502万
-$15,455/呎
-(24年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$675万
-$15,071/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$742万
-$14,954/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$673万
-$14,852/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$656万
-$15,048/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$506万
-$15,699/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$493万
-$15,083/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="H29" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$490万
-$15,083/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$674万
-$15,047/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$740万
-$14,923/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$657万
-$14,501/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$641万
-$14,693/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$477万
-$14,826/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G30" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$492万
-$15,061/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H30" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$490万
-$15,062/呎
-(24年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$672万
-$14,996/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$737万
-$14,865/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$654万
-$14,442/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$638万
-$14,633/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$503万
-$15,609/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G31" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$493万
-$15,086/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="H31" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$488万
-$15,000/呎
-(24年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$671万
-$14,971/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$736万
-$14,835/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$653万
-$14,413/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$637万
-$14,603/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$502万
-$15,581/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G32" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$490万
-$14,969/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="H32" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$486万
-$14,969/呎
-(25年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$670万
-$14,946/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$734万
-$14,804/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$652万
-$14,386/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$636万
-$14,576/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$474万
-$14,714/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G33" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$488万
-$14,939/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="H33" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$486万
-$14,938/呎
-(24年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$668万
-$14,922/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$733万
-$14,774/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$658万
-$14,521/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$634万
-$14,546/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$500万
-$15,519/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G34" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$488万
-$14,911/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H34" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$490万
-$15,080/呎
-(24年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$682万
-$15,234/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$740万
-$14,911/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$649万
-$14,327/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$633万
-$14,516/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$483万
-$14,991/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G35" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$487万
-$14,881/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="H35" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$484万
-$14,880/呎
-(25年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$666万
-$14,873/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C36" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$730万
-$14,714/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D36" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$648万
-$14,307/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E36" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$632万
-$14,495/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F36" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$471万
-$14,630/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G36" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$486万
-$14,850/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="H36" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$483万
-$14,849/呎
-(25年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$665万
-$14,848/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="C37" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$728万
-$14,683/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D37" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$647万
-$14,278/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E37" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$634万
-$14,539/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="F37" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$472万
-$14,674/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="G37" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$485万
-$14,823/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H37" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$482万
-$14,822/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B38" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$664万
-$14,824/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="C38" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$730万
-$14,726/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="D38" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$649万
-$14,320/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E38" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$633万
-$14,509/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$472万
-$14,646/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="G38" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$489万
-$14,960/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="H38" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$481万
-$14,791/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$663万
-$14,799/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C39" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$725万
-$14,623/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$645万
-$14,230/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E39" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$636万
-$14,580/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F39" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$468万
-$14,540/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G39" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$483万
-$14,771/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H39" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$491万
-$15,105/呎
-(24年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="65" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B40" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$661万
-$14,750/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C40" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$722万
-$14,565/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D40" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$642万
-$14,170/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E40" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$662万
-$15,174/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F40" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$493万
-$15,307/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G40" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$481万
-$14,713/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="H40" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$478万
-$14,714/呎
-(24年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="65" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B41" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$675万
-$15,060/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="C41" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$737万
-$14,867/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D41" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$641万
-$14,143/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E41" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$639万
-$14,656/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F41" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$465万
-$14,453/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G41" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$486万
-$14,847/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="H41" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$477万
-$14,683/呎
-(24年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="65" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B42" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$659万
-$14,701/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="C42" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$720万
-$14,508/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D42" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$639万
-$14,115/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E42" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$638万
-$14,626/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F42" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$464万
-$14,422/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G42" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$479万
-$14,651/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="H42" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$476万
-$14,652/呎
-(24年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="65" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B43" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$658万
-$14,676/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C43" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$718万
-$14,480/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D43" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$638万
-$14,086/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E43" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$622万
-$14,273/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F43" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$463万
-$14,391/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G43" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$478万
-$14,624/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="H43" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$475万
-$14,622/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="65" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B44" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$656万
-$14,652/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C44" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$725万
-$14,617/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D44" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$637万
-$14,068/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E44" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$622万
-$14,257/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F44" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$462万
-$14,360/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G44" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$477万
-$14,593/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="H44" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$474万
-$14,594/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="65" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B45" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$655万
-$14,627/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C45" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$715万
-$14,423/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D45" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$637万
-$14,057/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E45" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$621万
-$14,245/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F45" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$488万
-$15,143/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G45" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$476万
-$14,566/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="H45" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$484万
-$14,898/呎
-(24年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="65" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B46" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$654万
-$14,603/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C46" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$714万
-$14,395/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D46" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$636万
-$14,046/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E46" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$621万
-$14,234/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F46" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$471万
-$14,621/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G46" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$486万
-$14,865/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="H46" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$472万
-$14,535/呎
-(24年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="65" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B47" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$653万
-$14,578/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C47" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$713万
-$14,367/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D47" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$650万
-$14,353/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E47" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$620万
-$14,222/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F47" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$460万
-$14,270/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G47" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$502万
-$15,346/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H47" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$483万
-$14,849/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="65" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B48" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$651万
-$14,529/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="C48" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$710万
-$14,310/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D48" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$635万
-$14,013/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E48" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$633万
-$14,523/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F48" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$458万
-$14,214/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G48" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$473万
-$14,465/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="H48" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$470万
-$14,465/呎
-(24年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="65" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B49" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$650万
-$14,504/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="C49" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$708万
-$14,282/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D49" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$670万
-$14,797/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E49" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$619万
-$14,188/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F49" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$483万
-$14,991/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G49" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$472万
-$14,434/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="H49" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$469万
-$14,434/呎
-(24年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="65" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B50" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$649万
-$14,480/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C50" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$707万
-$14,254/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D50" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$637万
-$14,062/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E50" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$621万
-$14,248/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="F50" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$466万
-$14,478/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G50" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$471万
-$14,407/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="H50" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$518万
-$15,938/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="65" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B51" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$655万
-$14,618/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C51" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$706万
-$14,226/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D51" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$669万
-$14,775/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E51" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$618万
-$14,165/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F51" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$460万
-$14,292/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G51" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$481万
-$14,703/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="H51" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$467万
-$14,375/呎
-(24年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="65" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B52" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$650万
-$14,513/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C52" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$704万
-$14,198/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D52" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$633万
-$13,969/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E52" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$617万
-$14,154/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F52" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$459万
-$14,264/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G52" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$480万
-$14,673/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="H52" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$466万
-$14,351/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="65" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B53" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$649万
-$14,487/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C53" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$706万
-$14,240/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="D53" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$672万
-$14,826/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E53" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$620万
-$14,213/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="F53" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$455万
-$14,143/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="G53" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$471万
-$14,391/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="H53" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$465万
-$14,320/呎
-(25年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="65" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B54" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$652万
-$14,545/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C54" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$705万
-$14,212/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D54" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$635万
-$14,018/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="E54" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$680万
-$15,599/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F54" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$465万
-$14,438/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="G54" s="17" t="inlineStr">
-        <is>
-          <t>F | 327呎 (1房)
-$472万
-$14,443/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="H54" s="17" t="inlineStr">
-        <is>
-          <t>G | 325呎 (1房)
-$467万
-$14,372/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="65" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B55" s="17" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-$654万
-$14,506/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C55" s="17" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$720万
-$14,506/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D55" s="17" t="inlineStr">
-        <is>
-          <t>C | 415呎 (2房)
-$699万
-$16,834/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="E55" s="17" t="inlineStr">
-        <is>
-          <t>D | 400呎 (2房)
-$679万
-$16,982/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="F55" s="17" t="inlineStr">
-        <is>
-          <t>E | 283呎 (1房)
-$529万
-$18,678/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="G55" s="17" t="inlineStr">
-        <is>
-          <t>F | 288呎 (1房)
-$593万
-$20,604/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H55" s="17" t="inlineStr">
-        <is>
-          <t>G | 285呎 (1房)
-$536万
-$18,800/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H55"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Park Seasons - 2B座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>350 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>6 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>343 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>66/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$1,172万
-$21,827/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 315呎 (1房)
-$722万
-$22,930/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$964万
-$21,370/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$882万
-$20,176/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$682万
-$21,046/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$606万
-$18,771/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>G | 451呎 (2房)
-$966万
-$21,417/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>65/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$921万
-$17,147/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 315呎 (1房)
-$522万
-$16,578/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$782万
-$17,341/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$736万
-$16,835/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$509万
-$15,710/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$512万
-$15,848/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t>G | 451呎 (2房)
-$768万
-$17,020/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>63/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$915万
-$17,032/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 315呎 (1房)
-$521万
-$16,543/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$777万
-$17,228/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$732万
-$16,748/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$508万
-$15,679/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$511万
-$15,814/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t>G | 451呎 (2房)
-$762万
-$16,907/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>62/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$901万
-$16,771/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 315呎 (1房)
-$520万
-$16,514/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$765万
-$16,960/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$728万
-$16,652/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$504万
-$15,562/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$510万
-$15,786/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>G | 451呎 (2房)
-$761万
-$16,871/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>61/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$895万
-$16,659/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 315呎 (1房)
-$519万
-$16,483/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$760万
-$16,851/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$723万
-$16,538/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$498万
-$15,361/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$509万
-$15,759/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t>G | 451呎 (2房)
-$759万
-$16,834/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>60/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$893万
-$16,626/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 315呎 (1房)
-$518万
-$16,454/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$758万
-$16,814/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$718万
-$16,439/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$502万
-$15,509/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$508万
-$15,731/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t>G | 451呎 (2房)
-$729万
-$16,173/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>59/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$891万
-$16,590/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 315呎 (1房)
-$517万
-$16,425/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$757万
-$16,778/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$690万
-$15,792/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$502万
-$15,481/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$504万
-$15,616/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t>G | 451呎 (2房)
-$728万
-$16,140/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>58/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$890万
-$16,564/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 315呎 (1房)
-$516万
-$16,394/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$756万
-$16,754/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$689万
-$15,769/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$509万
-$15,710/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$506万
-$15,672/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>G | 451呎 (2房)
-$727万
-$16,115/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>57/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$886万
-$16,495/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 315呎 (1房)
-$514万
-$16,333/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$724万
-$16,064/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$686万
-$15,703/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$499万
-$15,395/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$502万
-$15,529/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>G | 451呎 (2房)
-$724万
-$16,047/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>56/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$884万
-$16,462/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 315呎 (1房)
-$514万
-$16,305/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$723万
-$16,031/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$685万
-$15,670/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$495万
-$15,281/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$498万
-$15,415/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H15" s="17" t="inlineStr">
-        <is>
-          <t>G | 451呎 (2房)
-$722万
-$16,013/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>55/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$882万
-$16,428/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 315呎 (1房)
-$513万
-$16,273/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$722万
-$16,007/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$684万
-$15,645/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$494万
-$15,250/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$497万
-$15,384/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H16" s="17" t="inlineStr">
-        <is>
-          <t>G | 451呎 (2房)
-$721万
-$15,989/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>53/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$880万
-$16,393/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 315呎 (1房)
-$512万
-$16,244/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$697万
-$15,459/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$675万
-$15,455/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$490万
-$15,139/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$496万
-$15,356/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t>G | 451呎 (2房)
-$720万
-$15,953/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>52/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$845万
-$15,732/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 315呎 (1房)
-$511万
-$16,216/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$696万
-$15,428/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$670万
-$15,336/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$490万
-$15,111/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$495万
-$15,331/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t>G | 451呎 (2房)
-$718万
-$15,922/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>51/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$843万
-$15,698/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 315呎 (1房)
-$510万
-$16,187/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$694万
-$15,395/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$665万
-$15,220/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$489万
-$15,083/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$492万
-$15,217/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
-        <is>
-          <t>G | 451呎 (2房)
-$716万
-$15,885/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>50/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$841万
-$15,665/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 315呎 (1房)
-$509万
-$16,152/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$693万
-$15,361/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$656万
-$15,018/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$488万
-$15,052/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$490万
-$15,186/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>G | 451呎 (2房)
-$715万
-$15,856/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>48/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$840万
-$15,641/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$508万
-$16,175/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$696万
-$15,426/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$655万
-$14,993/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$487万
-$15,028/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$487万
-$15,074/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$533万
-$15,899/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>47/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$870万
-$16,196/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$506万
-$16,118/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$689万
-$15,273/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$656万
-$15,000/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$488万
-$15,059/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$488万
-$15,105/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$531万
-$15,842/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>46/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$836万
-$15,574/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$485万
-$15,436/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$692万
-$15,344/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$662万
-$15,137/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$487万
-$15,043/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$487万
-$15,090/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H23" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$530万
-$15,812/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>45/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$833万
-$15,512/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$484万
-$15,408/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$691万
-$15,313/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$656万
-$15,023/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$486万
-$14,988/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$486万
-$15,062/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H24" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$529万
-$15,785/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>43/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$831万
-$15,480/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$483万
-$15,379/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$689万
-$15,282/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$652万
-$14,908/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$482万
-$14,873/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$483万
-$14,950/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H25" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$528万
-$15,758/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$830万
-$15,449/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$482万
-$15,347/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$684万
-$15,173/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$647万
-$14,801/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$481万
-$14,846/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$485万
-$15,006/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$527万
-$15,731/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$828万
-$15,419/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$481万
-$15,322/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$687万
-$15,228/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$646万
-$14,773/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$486万
-$14,985/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$481万
-$14,895/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="H27" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$546万
-$16,313/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$826万
-$15,387/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$483万
-$15,379/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$686万
-$15,200/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$644万
-$14,744/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$479万
-$14,790/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="G28" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$480万
-$14,867/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H28" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$525万
-$15,678/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$825万
-$15,358/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$479万
-$15,261/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$680万
-$15,082/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$643万
-$14,714/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$478万
-$14,762/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$479万
-$14,836/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H29" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$524万
-$15,645/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$842万
-$15,683/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$478万
-$15,232/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$679万
-$15,060/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$657万
-$15,025/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$477万
-$14,735/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="G30" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$478万
-$14,808/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="H30" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$523万
-$15,618/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$820万
-$15,272/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$477万
-$15,178/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$676万
-$15,000/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$640万
-$14,634/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$476万
-$14,679/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="G31" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$477万
-$14,755/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="H31" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$522万
-$15,570/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$820万
-$15,272/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$476万
-$15,146/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$675万
-$14,971/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$638万
-$14,604/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$475万
-$14,651/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="G32" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$476万
-$14,724/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="H32" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$521万
-$15,552/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$817万
-$15,212/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$474万
-$15,089/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$672万
-$14,911/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$637万
-$14,574/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$474万
-$14,623/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="G33" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$475万
-$14,697/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="H33" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$520万
-$15,531/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$815万
-$15,182/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$473万
-$15,061/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$671万
-$14,880/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$650万
-$14,876/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$473万
-$14,596/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="G34" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$474万
-$14,669/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="H34" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$520万
-$15,510/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$814万
-$15,151/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$472万
-$15,032/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$670万
-$14,851/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$634万
-$14,517/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$472万
-$14,568/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="G35" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$473万
-$14,644/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="H35" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$520万
-$15,507/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$814万
-$15,166/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="C36" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$472万
-$15,045/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D36" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$671万
-$14,869/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E36" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$634万
-$14,506/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F36" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$472万
-$14,556/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G36" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$472万
-$14,625/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="H36" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$498万
-$14,860/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$823万
-$15,324/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="C37" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$472万
-$15,035/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D37" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$670万
-$14,858/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="E37" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$634万
-$14,497/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F37" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$471万
-$14,540/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G37" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$472万
-$14,616/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H37" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$498万
-$14,851/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B38" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$855万
-$15,916/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="C38" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$469万
-$14,943/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D38" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$667万
-$14,798/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="E38" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$631万
-$14,437/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$469万
-$14,481/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="G38" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$471万
-$14,585/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="H38" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$496万
-$14,821/呎
-(25年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$879万
-$16,365/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C39" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$474万
-$15,080/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$666万
-$14,778/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="E39" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$637万
-$14,579/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="F39" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$474万
-$14,614/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="G39" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$470万
-$14,554/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H39" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$496万
-$14,800/呎
-(25年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="65" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B40" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$804万
-$14,980/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C40" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$466万
-$14,854/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D40" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$679万
-$15,051/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="E40" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$628万
-$14,359/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F40" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$477万
-$14,722/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="G40" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$468万
-$14,498/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H40" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$494万
-$14,740/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="65" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B41" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$803万
-$14,948/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="C41" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$465万
-$14,822/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="D41" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$662万
-$14,687/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="E41" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$626万
-$14,332/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="F41" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$465万
-$14,364/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="G41" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$467万
-$14,464/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H41" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$493万
-$14,710/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="65" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B42" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$803万
-$14,948/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="C42" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$465万
-$14,818/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D42" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$661万
-$14,659/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E42" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$626万
-$14,332/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F42" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$465万
-$14,361/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="G42" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$466万
-$14,437/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H42" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$492万
-$14,684/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="65" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B43" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$801万
-$14,918/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="C43" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$470万
-$14,955/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="D43" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$660万
-$14,630/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="E43" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$625万
-$14,300/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F43" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$464万
-$14,330/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G43" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$465万
-$14,402/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H43" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$491万
-$14,651/呎
-(25年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="65" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B44" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$800万
-$14,888/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="C44" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$463万
-$14,755/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D44" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$660万
-$14,630/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="E44" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$624万
-$14,284/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F44" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$463万
-$14,299/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G44" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$464万
-$14,372/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H44" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$490万
-$14,624/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="65" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B45" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$796万
-$14,831/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="C45" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$472万
-$15,029/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="D45" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$658万
-$14,601/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E45" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$622万
-$14,245/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="F45" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$461万
-$14,241/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="G45" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$462万
-$14,313/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H45" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$489万
-$14,594/呎
-(24年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="65" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B46" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$795万
-$14,801/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="C46" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$460万
-$14,662/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D46" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$655万
-$14,521/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="E46" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$622万
-$14,233/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="F46" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$460万
-$14,210/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="G46" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$461万
-$14,282/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H46" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$488万
-$14,564/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="65" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B47" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$794万
-$14,786/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="C47" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$460万
-$14,634/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="D47" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$654万
-$14,506/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="E47" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$636万
-$14,545/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="F47" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$486万
-$15,003/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="G47" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$460万
-$14,254/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H47" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$487万
-$14,549/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="65" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B48" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$792万
-$14,756/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="C48" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$459万
-$14,605/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D48" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$660万
-$14,641/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="E48" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$622万
-$14,229/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F48" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$464万
-$14,327/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="G48" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$469万
-$14,520/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H48" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$486万
-$14,493/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="65" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B49" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$791万
-$14,726/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C49" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$458万
-$14,576/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="D49" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$652万
-$14,448/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="E49" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$621万
-$14,215/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F49" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$484万
-$14,941/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G49" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$458万
-$14,170/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H49" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$484万
-$14,463/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="65" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B50" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$798万
-$14,864/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="C50" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$457万
-$14,548/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="D50" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$650万
-$14,421/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="E50" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$621万
-$14,204/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F50" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$457万
-$14,111/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G50" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$457万
-$14,142/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H50" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$504万
-$15,060/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="65" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B51" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$795万
-$14,804/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C51" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$465万
-$14,818/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D51" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$648万
-$14,361/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="E51" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$633万
-$14,485/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="F51" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$466万
-$14,373/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="G51" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$466万
-$14,433/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H51" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$504万
-$15,030/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="65" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B52" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$784万
-$14,609/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C52" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$454万
-$14,462/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="D52" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$646万
-$14,333/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E52" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$618万
-$14,153/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F52" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$454万
-$14,028/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="G52" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$455万
-$14,087/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H52" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$502万
-$15,000/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="65" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B53" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$783万
-$14,579/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="C53" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$453万
-$14,433/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D53" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$645万
-$14,306/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E53" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$618万
-$14,142/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F53" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$454万
-$13,997/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="G53" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$454万
-$14,059/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H53" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$502万
-$14,970/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="65" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B54" s="17" t="inlineStr">
-        <is>
-          <t>A | 537呎 (2房)
-$784万
-$14,609/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="C54" s="17" t="inlineStr">
-        <is>
-          <t>B | 314呎 (1房)
-$454万
-$14,462/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="D54" s="17" t="inlineStr">
-        <is>
-          <t>C | 451呎 (2房)
-$654万
-$14,497/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E54" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$620万
-$14,185/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F54" s="17" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$454万
-$14,028/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="G54" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$454万
-$14,059/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H54" s="17" t="inlineStr">
-        <is>
-          <t>G | 335呎 (1房)
-$500万
-$14,940/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="65" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B55" s="17" t="inlineStr">
-        <is>
-          <t>A | 499呎 (2房)
-$905万
-$18,133/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C55" s="17" t="inlineStr">
-        <is>
-          <t>B | 277呎 (1房)
-$544万
-$19,639/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D55" s="17" t="inlineStr">
-        <is>
-          <t>C | 413呎 (2房)
-$836万
-$20,245/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E55" s="17" t="inlineStr">
-        <is>
-          <t>D | 399呎 (2房)
-$706万
-$17,682/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F55" s="17" t="inlineStr">
-        <is>
-          <t>E | 286呎 (1房)
-$570万
-$19,944/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G55" s="17" t="inlineStr">
-        <is>
-          <t>F | 286呎 (1房)
-$574万
-$20,070/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H55" s="19" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-将军澳-Park Seasons.xlsx
+++ b/files/九龙-将军澳-Park Seasons.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2B座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +43,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +143,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +224,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +654,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -32059,4 +32239,6481 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 437呎 (2房)
+$945万
+$21,629/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$1015万
+$20,468/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$915万
+$20,199/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$882万
+$20,241/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$611万
+$18,969/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 481呎 (2房)
+$1014万
+$21,075/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 437呎 (2房)
+$757万
+$17,318/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$787万
+$15,861/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$685万
+$15,121/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$693万
+$15,888/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$511万
+$15,879/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 481呎 (2房)
+$819万
+$17,019/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 437呎 (2房)
+$756万
+$17,288/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$785万
+$15,829/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$684万
+$15,099/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$689万
+$15,796/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$513万
+$15,938/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>F | 481呎 (2房)
+$832万
+$17,297/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 437呎 (2房)
+$754万
+$17,256/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$784万
+$15,798/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$683万
+$15,077/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$684万
+$15,693/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$498万
+$15,469/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>F | 481呎 (2房)
+$781万
+$16,241/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 437呎 (2房)
+$753万
+$17,224/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$782万
+$15,768/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$698万
+$15,397/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$679万
+$15,571/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$508万
+$15,792/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 481呎 (2房)
+$780万
+$16,208/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 437呎 (2房)
+$723万
+$16,551/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$772万
+$15,560/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$681万
+$15,033/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$675万
+$15,477/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$496万
+$15,413/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 481呎 (2房)
+$778万
+$16,175/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 437呎 (2房)
+$750万
+$17,160/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$770万
+$15,530/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$680万
+$15,011/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$685万
+$15,706/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$507万
+$15,736/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 481呎 (2房)
+$806万
+$16,765/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 437呎 (2房)
+$749万
+$17,130/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$778万
+$15,677/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$679万
+$14,989/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$684万
+$15,681/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$506万
+$15,708/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 481呎 (2房)
+$775万
+$16,114/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 437呎 (2房)
+$746万
+$17,066/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$766万
+$15,438/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$677万
+$14,949/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$666万
+$15,271/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$504万
+$15,649/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 481呎 (2房)
+$802万
+$16,667/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 437呎 (2房)
+$745万
+$17,039/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$764万
+$15,407/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$676万
+$14,927/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$661万
+$15,154/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$503万
+$15,621/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 481呎 (2房)
+$770万
+$16,012/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 437呎 (2房)
+$704万
+$16,121/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$763万
+$15,377/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$675万
+$14,905/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$660万
+$15,128/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$491万
+$15,245/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 481呎 (2房)
+$769万
+$15,988/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 437呎 (2房)
+$695万
+$15,913/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$770万
+$15,520/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$674万
+$14,887/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$658万
+$15,096/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$498万
+$15,478/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 481呎 (2房)
+$767万
+$15,954/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 437呎 (2房)
+$706万
+$16,156/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$803万
+$16,185/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$674万
+$14,868/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$657万
+$15,064/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$497万
+$15,447/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>F | 481呎 (2房)
+$766万
+$15,921/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 437呎 (2房)
+$705万
+$16,126/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$758万
+$15,286/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$672万
+$14,837/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$656万
+$15,034/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$496万
+$15,419/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 481呎 (2房)
+$764万
+$15,886/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 437呎 (2房)
+$700万
+$16,009/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$800万
+$16,123/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$671万
+$14,806/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$654万
+$15,002/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$515万
+$15,994/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>F | 481呎 (2房)
+$763万
+$15,854/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr"/>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$687万
+$15,333/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$755万
+$15,226/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$685万
+$15,119/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$660万
+$15,147/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$498万
+$15,450/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$528万
+$16,159/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$500万
+$15,382/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$684万
+$15,272/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$752万
+$15,165/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$667万
+$14,720/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$650万
+$14,915/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$485万
+$15,050/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$499万
+$15,266/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$508万
+$15,646/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$694万
+$15,500/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$759万
+$15,306/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$681万
+$15,024/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$649万
+$14,885/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$486万
+$15,106/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$499万
+$15,248/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$496万
+$15,265/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$685万
+$15,297/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$766万
+$15,448/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$664万
+$14,660/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$648万
+$14,853/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$486万
+$15,081/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$498万
+$15,232/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$506万
+$15,582/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$684万
+$15,266/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$765万
+$15,417/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$663万
+$14,631/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$646万
+$14,826/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$482万
+$14,966/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$497万
+$15,205/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$494万
+$15,206/呎
+(25年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$679万
+$15,147/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$746万
+$15,044/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$662万
+$14,609/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$645万
+$14,803/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$481万
+$14,938/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$499万
+$15,260/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$493万
+$15,172/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$689万
+$15,377/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$753万
+$15,185/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$660万
+$14,581/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$644万
+$14,773/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$486万
+$15,078/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$498万
+$15,229/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$492万
+$15,142/呎
+(25年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$680万
+$15,183/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$743万
+$14,984/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$659万
+$14,552/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$643万
+$14,743/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$479万
+$14,882/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$497万
+$15,199/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$502万
+$15,455/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$675万
+$15,071/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$742万
+$14,954/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$673万
+$14,852/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$656万
+$15,048/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$506万
+$15,699/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$493万
+$15,083/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$490万
+$15,083/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$674万
+$15,047/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$740万
+$14,923/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$657万
+$14,501/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$641万
+$14,693/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$477万
+$14,826/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$492万
+$15,061/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$490万
+$15,062/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$672万
+$14,996/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$737万
+$14,865/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$654万
+$14,442/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$638万
+$14,633/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$503万
+$15,609/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$493万
+$15,086/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$488万
+$15,000/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$671万
+$14,971/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$736万
+$14,835/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$653万
+$14,413/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$637万
+$14,603/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$502万
+$15,581/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$490万
+$14,969/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="H31" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$486万
+$14,969/呎
+(25年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$670万
+$14,946/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$734万
+$14,804/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$652万
+$14,386/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$636万
+$14,576/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$474万
+$14,714/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$488万
+$14,939/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H32" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$486万
+$14,938/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$668万
+$14,922/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$733万
+$14,774/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$658万
+$14,521/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$634万
+$14,546/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$500万
+$15,519/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G33" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$488万
+$14,911/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H33" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$490万
+$15,080/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$682万
+$15,234/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$740万
+$14,911/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$649万
+$14,327/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$633万
+$14,516/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$483万
+$14,991/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G34" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$487万
+$14,881/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="H34" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$484万
+$14,880/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$666万
+$14,873/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C35" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$730万
+$14,714/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D35" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$648万
+$14,307/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E35" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$632万
+$14,495/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$471万
+$14,630/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G35" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$486万
+$14,850/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H35" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$483万
+$14,849/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B36" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$665万
+$14,848/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C36" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$728万
+$14,683/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$647万
+$14,278/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$634万
+$14,539/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$472万
+$14,674/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="G36" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$485万
+$14,823/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H36" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$482万
+$14,822/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$664万
+$14,824/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C37" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$730万
+$14,726/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D37" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$649万
+$14,320/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$633万
+$14,509/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$472万
+$14,646/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="G37" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$489万
+$14,960/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="H37" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$481万
+$14,791/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B38" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$663万
+$14,799/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$725万
+$14,623/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$645万
+$14,230/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$636万
+$14,580/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$468万
+$14,540/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G38" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$483万
+$14,771/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H38" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$491万
+$15,105/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B39" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$661万
+$14,750/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C39" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$722万
+$14,565/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D39" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$642万
+$14,170/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E39" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$662万
+$15,174/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F39" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$493万
+$15,307/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G39" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$481万
+$14,713/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H39" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$478万
+$14,714/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="58" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B40" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$675万
+$15,060/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$737万
+$14,867/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D40" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$641万
+$14,143/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E40" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$639万
+$14,656/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F40" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$465万
+$14,453/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G40" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$486万
+$14,847/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H40" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$477万
+$14,683/呎
+(24年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B41" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$659万
+$14,701/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$720万
+$14,508/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D41" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$639万
+$14,115/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E41" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$638万
+$14,626/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F41" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$464万
+$14,422/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G41" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$479万
+$14,651/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H41" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$476万
+$14,652/呎
+(24年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="58" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B42" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$658万
+$14,676/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$718万
+$14,480/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D42" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$638万
+$14,086/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E42" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$622万
+$14,273/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F42" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$463万
+$14,391/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G42" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$478万
+$14,624/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H42" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$475万
+$14,622/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="58" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B43" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$656万
+$14,652/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$725万
+$14,617/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D43" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$637万
+$14,068/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E43" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$622万
+$14,257/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F43" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$462万
+$14,360/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G43" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$477万
+$14,593/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H43" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$474万
+$14,594/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="58" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B44" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$655万
+$14,627/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$715万
+$14,423/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D44" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$637万
+$14,057/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E44" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$621万
+$14,245/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F44" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$488万
+$15,143/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G44" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$476万
+$14,566/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H44" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$484万
+$14,898/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="58" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B45" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$654万
+$14,603/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$714万
+$14,395/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D45" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$636万
+$14,046/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E45" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$621万
+$14,234/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F45" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$471万
+$14,621/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G45" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$486万
+$14,865/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H45" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$472万
+$14,535/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="58" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B46" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$653万
+$14,578/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$713万
+$14,367/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D46" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$650万
+$14,353/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E46" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$620万
+$14,222/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F46" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$460万
+$14,270/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G46" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$502万
+$15,346/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H46" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$483万
+$14,849/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="58" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B47" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$651万
+$14,529/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="C47" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$710万
+$14,310/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D47" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$635万
+$14,013/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E47" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$633万
+$14,523/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F47" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$458万
+$14,214/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G47" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$473万
+$14,465/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H47" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$470万
+$14,465/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="58" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B48" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$650万
+$14,504/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$708万
+$14,282/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D48" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$670万
+$14,797/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E48" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$619万
+$14,188/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F48" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$483万
+$14,991/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G48" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$472万
+$14,434/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H48" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$469万
+$14,434/呎
+(24年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="58" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B49" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$649万
+$14,480/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C49" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$707万
+$14,254/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D49" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$637万
+$14,062/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E49" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$621万
+$14,248/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F49" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$466万
+$14,478/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G49" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$471万
+$14,407/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H49" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$518万
+$15,938/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="58" customHeight="1">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B50" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$655万
+$14,618/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C50" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$706万
+$14,226/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D50" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$669万
+$14,775/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E50" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$618万
+$14,165/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F50" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$460万
+$14,292/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G50" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$481万
+$14,703/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H50" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$467万
+$14,375/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="58" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B51" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$650万
+$14,513/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C51" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$704万
+$14,198/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D51" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$633万
+$13,969/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E51" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$617万
+$14,154/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F51" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$459万
+$14,264/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G51" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$480万
+$14,673/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H51" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$466万
+$14,351/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="58" customHeight="1">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B52" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$649万
+$14,487/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C52" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$706万
+$14,240/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D52" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$672万
+$14,826/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E52" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$620万
+$14,213/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F52" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$455万
+$14,143/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="G52" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$471万
+$14,391/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="H52" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$465万
+$14,320/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="58" customHeight="1">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B53" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$652万
+$14,545/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C53" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$705万
+$14,212/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D53" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$635万
+$14,018/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="E53" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$680万
+$15,599/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F53" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$465万
+$14,438/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="G53" s="21" t="inlineStr">
+        <is>
+          <t>F | 327呎 (1房)
+$472万
+$14,443/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H53" s="21" t="inlineStr">
+        <is>
+          <t>G | 325呎 (1房)
+$467万
+$14,372/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="58" customHeight="1">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B54" s="21" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+$654万
+$14,506/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C54" s="21" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$720万
+$14,506/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D54" s="21" t="inlineStr">
+        <is>
+          <t>C | 415呎 (2房)
+$699万
+$16,834/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="E54" s="21" t="inlineStr">
+        <is>
+          <t>D | 400呎 (2房)
+$679万
+$16,982/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F54" s="21" t="inlineStr">
+        <is>
+          <t>E | 283呎 (1房)
+$529万
+$18,678/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="G54" s="21" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$593万
+$20,604/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H54" s="21" t="inlineStr">
+        <is>
+          <t>G | 285呎 (1房)
+$536万
+$18,800/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$1172万
+$21,827/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 315呎 (1房)
+$722万
+$22,930/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$964万
+$21,370/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$882万
+$20,176/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$682万
+$21,046/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$606万
+$18,771/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 451呎 (2房)
+$966万
+$21,417/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$921万
+$17,147/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 315呎 (1房)
+$522万
+$16,578/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$782万
+$17,341/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$736万
+$16,835/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$509万
+$15,710/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$512万
+$15,848/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 451呎 (2房)
+$768万
+$17,020/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$915万
+$17,032/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 315呎 (1房)
+$521万
+$16,543/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$777万
+$17,228/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$732万
+$16,748/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$508万
+$15,679/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$511万
+$15,814/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>G | 451呎 (2房)
+$762万
+$16,907/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$901万
+$16,771/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 315呎 (1房)
+$520万
+$16,514/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$765万
+$16,960/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$728万
+$16,652/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$504万
+$15,562/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$510万
+$15,786/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>G | 451呎 (2房)
+$761万
+$16,871/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$895万
+$16,659/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 315呎 (1房)
+$519万
+$16,483/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$760万
+$16,851/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$723万
+$16,538/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$498万
+$15,361/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$509万
+$15,759/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 451呎 (2房)
+$759万
+$16,834/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$893万
+$16,626/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 315呎 (1房)
+$518万
+$16,454/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$758万
+$16,814/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$718万
+$16,439/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$502万
+$15,509/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$508万
+$15,731/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>G | 451呎 (2房)
+$729万
+$16,173/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$891万
+$16,590/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 315呎 (1房)
+$517万
+$16,425/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$757万
+$16,778/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$690万
+$15,792/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$502万
+$15,481/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$504万
+$15,616/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>G | 451呎 (2房)
+$728万
+$16,140/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$890万
+$16,564/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 315呎 (1房)
+$516万
+$16,394/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$756万
+$16,754/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$689万
+$15,769/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$509万
+$15,710/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$506万
+$15,672/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 451呎 (2房)
+$727万
+$16,115/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$886万
+$16,495/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 315呎 (1房)
+$514万
+$16,333/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$724万
+$16,064/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$686万
+$15,703/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$499万
+$15,395/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$502万
+$15,529/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>G | 451呎 (2房)
+$724万
+$16,047/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$884万
+$16,462/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 315呎 (1房)
+$514万
+$16,305/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$723万
+$16,031/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$685万
+$15,670/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$495万
+$15,281/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$498万
+$15,415/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>G | 451呎 (2房)
+$722万
+$16,013/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$882万
+$16,428/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 315呎 (1房)
+$513万
+$16,273/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$722万
+$16,007/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$684万
+$15,645/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$494万
+$15,250/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$497万
+$15,384/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 451呎 (2房)
+$721万
+$15,989/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$880万
+$16,393/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 315呎 (1房)
+$512万
+$16,244/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$697万
+$15,459/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$675万
+$15,455/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$490万
+$15,139/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$496万
+$15,356/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>G | 451呎 (2房)
+$720万
+$15,953/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$845万
+$15,732/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 315呎 (1房)
+$511万
+$16,216/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$696万
+$15,428/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$670万
+$15,336/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$490万
+$15,111/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$495万
+$15,331/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>G | 451呎 (2房)
+$718万
+$15,922/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$843万
+$15,698/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 315呎 (1房)
+$510万
+$16,187/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$694万
+$15,395/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$665万
+$15,220/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$489万
+$15,083/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$492万
+$15,217/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 451呎 (2房)
+$716万
+$15,885/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$841万
+$15,665/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 315呎 (1房)
+$509万
+$16,152/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$693万
+$15,361/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$656万
+$15,018/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$488万
+$15,052/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$490万
+$15,186/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>G | 451呎 (2房)
+$715万
+$15,856/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$840万
+$15,641/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$508万
+$16,175/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$696万
+$15,426/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$655万
+$14,993/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$487万
+$15,028/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$487万
+$15,074/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$533万
+$15,899/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$870万
+$16,196/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$506万
+$16,118/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$689万
+$15,273/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$656万
+$15,000/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$488万
+$15,059/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$488万
+$15,105/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$531万
+$15,842/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$836万
+$15,574/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$485万
+$15,436/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$692万
+$15,344/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$662万
+$15,137/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$487万
+$15,043/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$487万
+$15,090/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$530万
+$15,812/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$833万
+$15,512/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$484万
+$15,408/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$691万
+$15,313/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$656万
+$15,023/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$486万
+$14,988/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$486万
+$15,062/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$529万
+$15,785/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$831万
+$15,480/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$483万
+$15,379/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$689万
+$15,282/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$652万
+$14,908/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$482万
+$14,873/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$483万
+$14,950/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$528万
+$15,758/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$830万
+$15,449/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$482万
+$15,347/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$684万
+$15,173/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$647万
+$14,801/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$481万
+$14,846/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$485万
+$15,006/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$527万
+$15,731/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$828万
+$15,419/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$481万
+$15,322/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$687万
+$15,228/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$646万
+$14,773/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$486万
+$14,985/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$481万
+$14,895/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$546万
+$16,313/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$826万
+$15,387/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$483万
+$15,379/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$686万
+$15,200/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$644万
+$14,744/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$479万
+$14,790/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$480万
+$14,867/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$525万
+$15,678/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$825万
+$15,358/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$479万
+$15,261/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$680万
+$15,082/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$643万
+$14,714/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$478万
+$14,762/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$479万
+$14,836/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$524万
+$15,645/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$842万
+$15,683/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$478万
+$15,232/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$679万
+$15,060/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$657万
+$15,025/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$477万
+$14,735/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$478万
+$14,808/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$523万
+$15,618/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$820万
+$15,272/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$477万
+$15,178/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$676万
+$15,000/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$640万
+$14,634/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$476万
+$14,679/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$477万
+$14,755/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$522万
+$15,570/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$820万
+$15,272/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$476万
+$15,146/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$675万
+$14,971/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$638万
+$14,604/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$475万
+$14,651/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$476万
+$14,724/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="H31" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$521万
+$15,552/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$817万
+$15,212/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$474万
+$15,089/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$672万
+$14,911/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$637万
+$14,574/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$474万
+$14,623/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$475万
+$14,697/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="H32" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$520万
+$15,531/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$815万
+$15,182/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$473万
+$15,061/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$671万
+$14,880/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$650万
+$14,876/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$473万
+$14,596/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G33" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$474万
+$14,669/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="H33" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$520万
+$15,510/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$814万
+$15,151/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$472万
+$15,032/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$670万
+$14,851/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$634万
+$14,517/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$472万
+$14,568/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G34" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$473万
+$14,644/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="H34" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$520万
+$15,507/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$814万
+$15,166/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C35" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$472万
+$15,045/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D35" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$671万
+$14,869/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E35" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$634万
+$14,506/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$472万
+$14,556/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G35" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$472万
+$14,625/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="H35" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$498万
+$14,860/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B36" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$823万
+$15,324/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C36" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$472万
+$15,035/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$670万
+$14,858/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$634万
+$14,497/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$471万
+$14,540/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G36" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$472万
+$14,616/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H36" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$498万
+$14,851/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$855万
+$15,916/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="C37" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$469万
+$14,943/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D37" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$667万
+$14,798/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$631万
+$14,437/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$469万
+$14,481/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="G37" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$471万
+$14,585/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="H37" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$496万
+$14,821/呎
+(25年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B38" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$879万
+$16,365/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$474万
+$15,080/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$666万
+$14,778/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$637万
+$14,579/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$474万
+$14,614/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="G38" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$470万
+$14,554/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H38" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$496万
+$14,800/呎
+(25年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B39" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$804万
+$14,980/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C39" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$466万
+$14,854/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D39" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$679万
+$15,051/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="E39" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$628万
+$14,359/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F39" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$477万
+$14,722/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="G39" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$468万
+$14,498/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H39" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$494万
+$14,740/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="58" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B40" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$803万
+$14,948/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$465万
+$14,822/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="D40" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$662万
+$14,687/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="E40" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$626万
+$14,332/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="F40" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$465万
+$14,364/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="G40" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$467万
+$14,464/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H40" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$493万
+$14,710/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B41" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$803万
+$14,948/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$465万
+$14,818/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D41" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$661万
+$14,659/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E41" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$626万
+$14,332/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F41" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$465万
+$14,361/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G41" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$466万
+$14,437/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H41" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$492万
+$14,684/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="58" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B42" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$801万
+$14,918/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$470万
+$14,955/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D42" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$660万
+$14,630/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="E42" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$625万
+$14,300/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F42" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$464万
+$14,330/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G42" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$465万
+$14,402/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H42" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$491万
+$14,651/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="58" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B43" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$800万
+$14,888/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$463万
+$14,755/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D43" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$660万
+$14,630/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E43" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$624万
+$14,284/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F43" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$463万
+$14,299/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G43" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$464万
+$14,372/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H43" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$490万
+$14,624/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="58" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B44" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$796万
+$14,831/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$472万
+$15,029/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="D44" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$658万
+$14,601/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E44" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$622万
+$14,245/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="F44" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$461万
+$14,241/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="G44" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$462万
+$14,313/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H44" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$489万
+$14,594/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="58" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B45" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$795万
+$14,801/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$460万
+$14,662/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D45" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$655万
+$14,521/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="E45" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$622万
+$14,233/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="F45" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$460万
+$14,210/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="G45" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$461万
+$14,282/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H45" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$488万
+$14,564/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="58" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B46" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$794万
+$14,786/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$460万
+$14,634/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="D46" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$654万
+$14,506/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="E46" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$636万
+$14,545/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="F46" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$486万
+$15,003/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="G46" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$460万
+$14,254/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H46" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$487万
+$14,549/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="58" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B47" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$792万
+$14,756/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C47" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$459万
+$14,605/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D47" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$660万
+$14,641/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E47" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$622万
+$14,229/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F47" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$464万
+$14,327/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G47" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$469万
+$14,520/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H47" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$486万
+$14,493/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="58" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B48" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$791万
+$14,726/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$458万
+$14,576/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D48" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$652万
+$14,448/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="E48" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$621万
+$14,215/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F48" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$484万
+$14,941/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G48" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$458万
+$14,170/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H48" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$484万
+$14,463/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="58" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B49" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$798万
+$14,864/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C49" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$457万
+$14,548/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D49" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$650万
+$14,421/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="E49" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$621万
+$14,204/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F49" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$457万
+$14,111/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G49" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$457万
+$14,142/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H49" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$504万
+$15,060/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="58" customHeight="1">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B50" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$795万
+$14,804/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C50" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$465万
+$14,818/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D50" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$648万
+$14,361/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="E50" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$633万
+$14,485/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="F50" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$466万
+$14,373/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="G50" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$466万
+$14,433/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H50" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$504万
+$15,030/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="58" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B51" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$784万
+$14,609/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C51" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$454万
+$14,462/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D51" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$646万
+$14,333/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E51" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$618万
+$14,153/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F51" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$454万
+$14,028/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="G51" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$455万
+$14,087/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H51" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$502万
+$15,000/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="58" customHeight="1">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B52" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$783万
+$14,579/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C52" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$453万
+$14,433/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D52" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$645万
+$14,306/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E52" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$618万
+$14,142/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F52" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$454万
+$13,997/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="G52" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$454万
+$14,059/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H52" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$502万
+$14,970/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="58" customHeight="1">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B53" s="21" t="inlineStr">
+        <is>
+          <t>A | 537呎 (2房)
+$784万
+$14,609/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C53" s="21" t="inlineStr">
+        <is>
+          <t>B | 314呎 (1房)
+$454万
+$14,462/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D53" s="21" t="inlineStr">
+        <is>
+          <t>C | 451呎 (2房)
+$654万
+$14,497/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E53" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$620万
+$14,185/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F53" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$454万
+$14,028/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G53" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$454万
+$14,059/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H53" s="21" t="inlineStr">
+        <is>
+          <t>G | 335呎 (1房)
+$500万
+$14,940/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="58" customHeight="1">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B54" s="21" t="inlineStr">
+        <is>
+          <t>A | 499呎 (2房)
+$905万
+$18,133/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C54" s="21" t="inlineStr">
+        <is>
+          <t>B | 277呎 (1房)
+$544万
+$19,639/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D54" s="21" t="inlineStr">
+        <is>
+          <t>C | 413呎 (2房)
+$836万
+$20,245/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E54" s="21" t="inlineStr">
+        <is>
+          <t>D | 399呎 (2房)
+$706万
+$17,682/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F54" s="21" t="inlineStr">
+        <is>
+          <t>E | 286呎 (1房)
+$570万
+$19,944/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G54" s="21" t="inlineStr">
+        <is>
+          <t>F | 286呎 (1房)
+$574万
+$20,070/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H54" s="23" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-将军澳-Park Seasons.xlsx
+++ b/files/九龙-将军澳-Park Seasons.xlsx
@@ -654,7 +654,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
